--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396044</v>
+        <v>113396043</v>
       </c>
       <c r="B2" t="n">
         <v>56765</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577614</v>
+        <v>577704</v>
       </c>
       <c r="R2" t="n">
-        <v>6966377</v>
+        <v>6965948</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396043</v>
+        <v>113396052</v>
       </c>
       <c r="B3" t="n">
         <v>56765</v>
@@ -816,16 +816,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577704</v>
+        <v>577991</v>
       </c>
       <c r="R3" t="n">
-        <v>6965948</v>
+        <v>6965958</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +866,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396052</v>
+        <v>113396050</v>
       </c>
       <c r="B4" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +908,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -923,24 +926,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577991</v>
+        <v>577840</v>
       </c>
       <c r="R4" t="n">
-        <v>6965958</v>
+        <v>6966452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396050</v>
+        <v>113396044</v>
       </c>
       <c r="B5" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577840</v>
+        <v>577614</v>
       </c>
       <c r="R5" t="n">
-        <v>6966452</v>
+        <v>6966377</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396043</v>
+        <v>113396052</v>
       </c>
       <c r="B2" t="n">
         <v>56765</v>
@@ -709,16 +709,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577704</v>
+        <v>577991</v>
       </c>
       <c r="R2" t="n">
-        <v>6965948</v>
+        <v>6965958</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396052</v>
+        <v>113396050</v>
       </c>
       <c r="B3" t="n">
-        <v>56765</v>
+        <v>56781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +801,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -816,24 +819,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577991</v>
+        <v>577840</v>
       </c>
       <c r="R3" t="n">
-        <v>6965958</v>
+        <v>6966452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +861,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396050</v>
+        <v>113396043</v>
       </c>
       <c r="B4" t="n">
-        <v>56781</v>
+        <v>56765</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,16 +908,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577840</v>
+        <v>577704</v>
       </c>
       <c r="R4" t="n">
-        <v>6966452</v>
+        <v>6965948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396052</v>
+        <v>113396044</v>
       </c>
       <c r="B2" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,24 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577991</v>
+        <v>577614</v>
       </c>
       <c r="R2" t="n">
-        <v>6965958</v>
+        <v>6966377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396050</v>
+        <v>113396043</v>
       </c>
       <c r="B3" t="n">
-        <v>56781</v>
+        <v>56766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577840</v>
+        <v>577704</v>
       </c>
       <c r="R3" t="n">
-        <v>6966452</v>
+        <v>6965948</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396043</v>
+        <v>113396050</v>
       </c>
       <c r="B4" t="n">
-        <v>56765</v>
+        <v>56782</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577704</v>
+        <v>577840</v>
       </c>
       <c r="R4" t="n">
-        <v>6965948</v>
+        <v>6966452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396044</v>
+        <v>113396052</v>
       </c>
       <c r="B5" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,16 +1030,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577614</v>
+        <v>577991</v>
       </c>
       <c r="R5" t="n">
-        <v>6966377</v>
+        <v>6965958</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,11 +1080,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396044</v>
+        <v>113396043</v>
       </c>
       <c r="B2" t="n">
         <v>56766</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577614</v>
+        <v>577704</v>
       </c>
       <c r="R2" t="n">
-        <v>6966377</v>
+        <v>6965948</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396043</v>
+        <v>113396050</v>
       </c>
       <c r="B3" t="n">
-        <v>56766</v>
+        <v>56782</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577704</v>
+        <v>577840</v>
       </c>
       <c r="R3" t="n">
-        <v>6965948</v>
+        <v>6966452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396050</v>
+        <v>113396052</v>
       </c>
       <c r="B4" t="n">
-        <v>56782</v>
+        <v>56766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -923,16 +923,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577840</v>
+        <v>577991</v>
       </c>
       <c r="R4" t="n">
-        <v>6966452</v>
+        <v>6965958</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +973,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396052</v>
+        <v>113396044</v>
       </c>
       <c r="B5" t="n">
         <v>56766</v>
@@ -1030,24 +1033,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577991</v>
+        <v>577614</v>
       </c>
       <c r="R5" t="n">
-        <v>6965958</v>
+        <v>6966377</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,6 +1075,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396043</v>
+        <v>113396044</v>
       </c>
       <c r="B2" t="n">
         <v>56766</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577704</v>
+        <v>577614</v>
       </c>
       <c r="R2" t="n">
-        <v>6965948</v>
+        <v>6966377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396052</v>
+        <v>113396043</v>
       </c>
       <c r="B4" t="n">
         <v>56766</v>
@@ -923,24 +923,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577991</v>
+        <v>577704</v>
       </c>
       <c r="R4" t="n">
-        <v>6965958</v>
+        <v>6965948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396044</v>
+        <v>113396052</v>
       </c>
       <c r="B5" t="n">
         <v>56766</v>
@@ -1033,16 +1030,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577614</v>
+        <v>577991</v>
       </c>
       <c r="R5" t="n">
-        <v>6966377</v>
+        <v>6965958</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,11 +1080,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396044</v>
+        <v>113396052</v>
       </c>
       <c r="B2" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,16 +709,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577614</v>
+        <v>577991</v>
       </c>
       <c r="R2" t="n">
-        <v>6966377</v>
+        <v>6965958</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396050</v>
+        <v>113396043</v>
       </c>
       <c r="B3" t="n">
-        <v>56782</v>
+        <v>56769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +801,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577840</v>
+        <v>577704</v>
       </c>
       <c r="R3" t="n">
-        <v>6966452</v>
+        <v>6965948</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +865,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396043</v>
+        <v>113396050</v>
       </c>
       <c r="B4" t="n">
-        <v>56766</v>
+        <v>56785</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +908,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -929,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577704</v>
+        <v>577840</v>
       </c>
       <c r="R4" t="n">
-        <v>6965948</v>
+        <v>6966452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396052</v>
+        <v>113396044</v>
       </c>
       <c r="B5" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,24 +1033,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577991</v>
+        <v>577614</v>
       </c>
       <c r="R5" t="n">
-        <v>6965958</v>
+        <v>6966377</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,6 +1075,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396052</v>
+        <v>113396050</v>
       </c>
       <c r="B2" t="n">
-        <v>56769</v>
+        <v>56785</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,24 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577991</v>
+        <v>577840</v>
       </c>
       <c r="R2" t="n">
-        <v>6965958</v>
+        <v>6966452</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -892,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396050</v>
+        <v>113396044</v>
       </c>
       <c r="B4" t="n">
-        <v>56785</v>
+        <v>56769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577840</v>
+        <v>577614</v>
       </c>
       <c r="R4" t="n">
-        <v>6966452</v>
+        <v>6966377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396044</v>
+        <v>113396052</v>
       </c>
       <c r="B5" t="n">
         <v>56769</v>
@@ -1033,16 +1030,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577614</v>
+        <v>577991</v>
       </c>
       <c r="R5" t="n">
-        <v>6966377</v>
+        <v>6965958</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,11 +1080,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113396050</v>
       </c>
       <c r="B2" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396043</v>
+        <v>113396044</v>
       </c>
       <c r="B3" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577704</v>
+        <v>577614</v>
       </c>
       <c r="R3" t="n">
-        <v>6965948</v>
+        <v>6966377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396044</v>
+        <v>113396043</v>
       </c>
       <c r="B4" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577614</v>
+        <v>577704</v>
       </c>
       <c r="R4" t="n">
-        <v>6966377</v>
+        <v>6965948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>113396052</v>
       </c>
       <c r="B5" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396050</v>
+        <v>113396044</v>
       </c>
       <c r="B2" t="n">
-        <v>56789</v>
+        <v>56773</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577840</v>
+        <v>577614</v>
       </c>
       <c r="R2" t="n">
-        <v>6966452</v>
+        <v>6966377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396044</v>
+        <v>113396043</v>
       </c>
       <c r="B3" t="n">
         <v>56773</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577614</v>
+        <v>577704</v>
       </c>
       <c r="R3" t="n">
-        <v>6966377</v>
+        <v>6965948</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396043</v>
+        <v>113396052</v>
       </c>
       <c r="B4" t="n">
         <v>56773</v>
@@ -923,16 +923,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577704</v>
+        <v>577991</v>
       </c>
       <c r="R4" t="n">
-        <v>6965948</v>
+        <v>6965958</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +973,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396052</v>
+        <v>113396050</v>
       </c>
       <c r="B5" t="n">
-        <v>56773</v>
+        <v>56789</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,16 +1015,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1030,24 +1033,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577991</v>
+        <v>577840</v>
       </c>
       <c r="R5" t="n">
-        <v>6965958</v>
+        <v>6966452</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,6 +1075,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396044</v>
+        <v>113396050</v>
       </c>
       <c r="B2" t="n">
-        <v>56773</v>
+        <v>56796</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577614</v>
+        <v>577840</v>
       </c>
       <c r="R2" t="n">
-        <v>6966377</v>
+        <v>6966452</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396043</v>
+        <v>113396044</v>
       </c>
       <c r="B3" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577704</v>
+        <v>577614</v>
       </c>
       <c r="R3" t="n">
-        <v>6965948</v>
+        <v>6966377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396052</v>
+        <v>113396043</v>
       </c>
       <c r="B4" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,24 +923,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577991</v>
+        <v>577704</v>
       </c>
       <c r="R4" t="n">
-        <v>6965958</v>
+        <v>6965948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396050</v>
+        <v>113396052</v>
       </c>
       <c r="B5" t="n">
-        <v>56789</v>
+        <v>56780</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,16 +1012,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1033,16 +1030,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577840</v>
+        <v>577991</v>
       </c>
       <c r="R5" t="n">
-        <v>6966452</v>
+        <v>6965958</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,11 +1080,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396050</v>
+        <v>113396052</v>
       </c>
       <c r="B2" t="n">
-        <v>56796</v>
+        <v>56782</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,16 +709,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577840</v>
+        <v>577991</v>
       </c>
       <c r="R2" t="n">
-        <v>6966452</v>
+        <v>6965958</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396044</v>
+        <v>113396050</v>
       </c>
       <c r="B3" t="n">
-        <v>56780</v>
+        <v>56798</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +801,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577614</v>
+        <v>577840</v>
       </c>
       <c r="R3" t="n">
-        <v>6966377</v>
+        <v>6966452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +865,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396043</v>
+        <v>113396044</v>
       </c>
       <c r="B4" t="n">
-        <v>56780</v>
+        <v>56782</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577704</v>
+        <v>577614</v>
       </c>
       <c r="R4" t="n">
-        <v>6965948</v>
+        <v>6966377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396052</v>
+        <v>113396043</v>
       </c>
       <c r="B5" t="n">
-        <v>56780</v>
+        <v>56782</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,24 +1033,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577991</v>
+        <v>577704</v>
       </c>
       <c r="R5" t="n">
-        <v>6965958</v>
+        <v>6965948</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,6 +1075,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113396052</v>
       </c>
       <c r="B2" t="n">
-        <v>56782</v>
+        <v>56810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>113396050</v>
       </c>
       <c r="B3" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396044</v>
+        <v>113396043</v>
       </c>
       <c r="B4" t="n">
-        <v>56782</v>
+        <v>56810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577614</v>
+        <v>577704</v>
       </c>
       <c r="R4" t="n">
-        <v>6966377</v>
+        <v>6965948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396043</v>
+        <v>113396044</v>
       </c>
       <c r="B5" t="n">
-        <v>56782</v>
+        <v>56810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577704</v>
+        <v>577614</v>
       </c>
       <c r="R5" t="n">
-        <v>6965948</v>
+        <v>6966377</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396052</v>
+        <v>113396050</v>
       </c>
       <c r="B2" t="n">
-        <v>56810</v>
+        <v>56826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,24 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577991</v>
+        <v>577840</v>
       </c>
       <c r="R2" t="n">
-        <v>6965958</v>
+        <v>6966452</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396050</v>
+        <v>113396052</v>
       </c>
       <c r="B3" t="n">
-        <v>56826</v>
+        <v>56810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,16 +816,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kråkstensjö, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577840</v>
+        <v>577991</v>
       </c>
       <c r="R3" t="n">
-        <v>6966452</v>
+        <v>6965958</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,11 +866,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396043</v>
+        <v>113396044</v>
       </c>
       <c r="B4" t="n">
         <v>56810</v>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577704</v>
+        <v>577614</v>
       </c>
       <c r="R4" t="n">
-        <v>6965948</v>
+        <v>6966377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396044</v>
+        <v>113396043</v>
       </c>
       <c r="B5" t="n">
         <v>56810</v>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577614</v>
+        <v>577704</v>
       </c>
       <c r="R5" t="n">
-        <v>6966377</v>
+        <v>6965948</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1104,6 +1104,745 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120348753</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kråkstensjö NÖ, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>577778</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6965996</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120348747</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kråkstensjö NÖ, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577916</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6965924</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120348752</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kråkstensjö NÖ, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>577776</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6966032</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120348755</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kråkstensjö NÖ, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577850</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6965952</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120348751</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kråkstensjö NÖ, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577917</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6965940</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120348749</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96891</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kråkstensjö NÖ, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>577670</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6966198</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120348748</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kråkstensjö NÖ, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>577838</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6966437</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348753</v>
+        <v>120348748</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,25 +1118,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577778</v>
+        <v>577838</v>
       </c>
       <c r="R6" t="n">
-        <v>6965996</v>
+        <v>6966437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,6 +1182,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348747</v>
+        <v>120348749</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>96891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,58 +1225,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kråkstensjö NÖ, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577916</v>
+        <v>577670</v>
       </c>
       <c r="R7" t="n">
-        <v>6965924</v>
+        <v>6966198</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1315,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348752</v>
+        <v>120348753</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1370,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577776</v>
+        <v>577778</v>
       </c>
       <c r="R8" t="n">
-        <v>6966032</v>
+        <v>6965996</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348751</v>
+        <v>120348747</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,38 +1531,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kråkstensjö NÖ, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577917</v>
+        <v>577916</v>
       </c>
       <c r="R10" t="n">
-        <v>6965940</v>
+        <v>6965924</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348749</v>
+        <v>120348752</v>
       </c>
       <c r="B11" t="n">
-        <v>96891</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,25 +1653,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1676,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577670</v>
+        <v>577776</v>
       </c>
       <c r="R11" t="n">
-        <v>6966198</v>
+        <v>6966032</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348748</v>
+        <v>120348751</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1750,25 +1755,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577838</v>
+        <v>577917</v>
       </c>
       <c r="R12" t="n">
-        <v>6966437</v>
+        <v>6965940</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,11 +1819,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348748</v>
+        <v>120348751</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,25 +1118,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577838</v>
+        <v>577917</v>
       </c>
       <c r="R6" t="n">
-        <v>6966437</v>
+        <v>6965940</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,11 +1182,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348749</v>
+        <v>120348753</v>
       </c>
       <c r="B7" t="n">
-        <v>96891</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,25 +1220,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577670</v>
+        <v>577778</v>
       </c>
       <c r="R7" t="n">
-        <v>6966198</v>
+        <v>6965996</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1310,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348753</v>
+        <v>120348752</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1355,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577778</v>
+        <v>577776</v>
       </c>
       <c r="R8" t="n">
-        <v>6965996</v>
+        <v>6966032</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348755</v>
+        <v>120348749</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>96891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1424,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577850</v>
+        <v>577670</v>
       </c>
       <c r="R9" t="n">
-        <v>6965952</v>
+        <v>6966198</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1641,7 +1636,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348752</v>
+        <v>120348755</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1681,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577776</v>
+        <v>577850</v>
       </c>
       <c r="R11" t="n">
-        <v>6966032</v>
+        <v>6965952</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1738,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348751</v>
+        <v>120348748</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,25 +1750,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577917</v>
+        <v>577838</v>
       </c>
       <c r="R12" t="n">
-        <v>6965940</v>
+        <v>6966437</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,6 +1814,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348751</v>
+        <v>120348748</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,25 +1118,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577917</v>
+        <v>577838</v>
       </c>
       <c r="R6" t="n">
-        <v>6965940</v>
+        <v>6966437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,6 +1182,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,7 +1213,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348753</v>
+        <v>120348752</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1248,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577778</v>
+        <v>577776</v>
       </c>
       <c r="R7" t="n">
-        <v>6965996</v>
+        <v>6966032</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1315,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348752</v>
+        <v>120348755</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1350,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577776</v>
+        <v>577850</v>
       </c>
       <c r="R8" t="n">
-        <v>6966032</v>
+        <v>6965952</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348749</v>
+        <v>120348751</v>
       </c>
       <c r="B9" t="n">
-        <v>96891</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577670</v>
+        <v>577917</v>
       </c>
       <c r="R9" t="n">
-        <v>6966198</v>
+        <v>6965940</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348747</v>
+        <v>120348753</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,58 +1531,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kråkstensjö NÖ, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577916</v>
+        <v>577778</v>
       </c>
       <c r="R10" t="n">
-        <v>6965924</v>
+        <v>6965996</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348755</v>
+        <v>120348747</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,38 +1633,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kråkstensjö NÖ, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577850</v>
+        <v>577916</v>
       </c>
       <c r="R11" t="n">
-        <v>6965952</v>
+        <v>6965924</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348748</v>
+        <v>120348749</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>96891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1750,25 +1755,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577838</v>
+        <v>577670</v>
       </c>
       <c r="R12" t="n">
-        <v>6966437</v>
+        <v>6966198</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,11 +1819,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348748</v>
+        <v>120348753</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,25 +1118,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577838</v>
+        <v>577778</v>
       </c>
       <c r="R6" t="n">
-        <v>6966437</v>
+        <v>6965996</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,11 +1182,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1208,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348752</v>
+        <v>120348755</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1253,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577776</v>
+        <v>577850</v>
       </c>
       <c r="R7" t="n">
-        <v>6966032</v>
+        <v>6965952</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1310,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348755</v>
+        <v>120348752</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1355,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577850</v>
+        <v>577776</v>
       </c>
       <c r="R8" t="n">
-        <v>6965952</v>
+        <v>6966032</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1519,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348753</v>
+        <v>120348748</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,25 +1526,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1559,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577778</v>
+        <v>577838</v>
       </c>
       <c r="R10" t="n">
-        <v>6965996</v>
+        <v>6966437</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,6 +1590,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348755</v>
+        <v>120348748</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,25 +1220,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577850</v>
+        <v>577838</v>
       </c>
       <c r="R7" t="n">
-        <v>6965952</v>
+        <v>6966437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,6 +1284,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348752</v>
+        <v>120348749</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>96891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,25 +1327,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577776</v>
+        <v>577670</v>
       </c>
       <c r="R8" t="n">
-        <v>6966032</v>
+        <v>6966198</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1514,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348748</v>
+        <v>120348752</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,25 +1531,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577838</v>
+        <v>577776</v>
       </c>
       <c r="R10" t="n">
-        <v>6966437</v>
+        <v>6966032</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,11 +1595,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348749</v>
+        <v>120348755</v>
       </c>
       <c r="B12" t="n">
-        <v>96891</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,25 +1755,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577670</v>
+        <v>577850</v>
       </c>
       <c r="R12" t="n">
-        <v>6966198</v>
+        <v>6965952</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348748</v>
+        <v>120348749</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>96891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,25 +1220,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577838</v>
+        <v>577670</v>
       </c>
       <c r="R7" t="n">
-        <v>6966437</v>
+        <v>6966198</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,11 +1284,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348749</v>
+        <v>120348747</v>
       </c>
       <c r="B8" t="n">
-        <v>96891</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,38 +1322,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kråkstensjö NÖ, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577670</v>
+        <v>577916</v>
       </c>
       <c r="R8" t="n">
-        <v>6966198</v>
+        <v>6965924</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1519,7 +1534,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348752</v>
+        <v>120348755</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1559,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577776</v>
+        <v>577850</v>
       </c>
       <c r="R10" t="n">
-        <v>6966032</v>
+        <v>6965952</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348747</v>
+        <v>120348748</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1637,16 +1652,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1654,37 +1669,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kråkstensjö NÖ, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577916</v>
+        <v>577838</v>
       </c>
       <c r="R11" t="n">
-        <v>6965924</v>
+        <v>6966437</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,6 +1712,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,7 +1743,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348755</v>
+        <v>120348752</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577850</v>
+        <v>577776</v>
       </c>
       <c r="R12" t="n">
-        <v>6965952</v>
+        <v>6966032</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -1106,7 +1106,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348753</v>
+        <v>120348751</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577778</v>
+        <v>577917</v>
       </c>
       <c r="R6" t="n">
-        <v>6965996</v>
+        <v>6965940</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348749</v>
+        <v>120348748</v>
       </c>
       <c r="B7" t="n">
-        <v>96891</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,25 +1220,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577670</v>
+        <v>577838</v>
       </c>
       <c r="R7" t="n">
-        <v>6966198</v>
+        <v>6966437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,6 +1284,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348747</v>
+        <v>120348749</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>96891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,58 +1327,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kråkstensjö NÖ, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577916</v>
+        <v>577670</v>
       </c>
       <c r="R8" t="n">
-        <v>6965924</v>
+        <v>6966198</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348751</v>
+        <v>120348747</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,38 +1429,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kråkstensjö NÖ, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577917</v>
+        <v>577916</v>
       </c>
       <c r="R9" t="n">
-        <v>6965940</v>
+        <v>6965924</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1636,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348748</v>
+        <v>120348752</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,25 +1653,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1676,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577838</v>
+        <v>577776</v>
       </c>
       <c r="R11" t="n">
-        <v>6966437</v>
+        <v>6966032</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,11 +1717,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,7 +1743,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348752</v>
+        <v>120348753</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577776</v>
+        <v>577778</v>
       </c>
       <c r="R12" t="n">
-        <v>6966032</v>
+        <v>6965996</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113396052</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>113396043</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>113396044</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>120348747</v>
       </c>
       <c r="B11" t="n">
-        <v>57335</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113396052</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>113396043</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>113396044</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>120348747</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113396052</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>113396043</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>113396044</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>120348747</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 45949-2023 artfynd.xlsx
+++ b/artfynd/A 45949-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113396052</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>113396043</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>113396044</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>120348747</v>
       </c>
       <c r="B11" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
